--- a/Sequence.xlsx
+++ b/Sequence.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\New Documents\Zachary\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Career\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3576EC42-F7D3-4E2D-9CCF-4FBFEF5C692F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED0977A-1446-4267-9F07-9BA87B43F021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{9C5A1693-2DD9-4A08-B439-7C8A3F7D239A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9C5A1693-2DD9-4A08-B439-7C8A3F7D239A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -153,12 +153,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,7 +821,7 @@
       <c r="B18" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>9</v>
       </c>
     </row>
